--- a/ig/DM-MARS-2026/ValueSet-JDV-J258-Departement.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-JDV-J258-Departement.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="259">
   <si>
     <t>Property</t>
   </si>
@@ -757,6 +757,30 @@
   </si>
   <si>
     <t>La Passion-Clipperton (989)</t>
+  </si>
+  <si>
+    <t>91352</t>
+  </si>
+  <si>
+    <t>Département D'Alger et Orleansville (91352)</t>
+  </si>
+  <si>
+    <t>92352</t>
+  </si>
+  <si>
+    <t>Département D'Oran et Bou Sfer (92352)</t>
+  </si>
+  <si>
+    <t>93352</t>
+  </si>
+  <si>
+    <t>Département de Constantine (93352)</t>
+  </si>
+  <si>
+    <t>94352</t>
+  </si>
+  <si>
+    <t>Sud de l'Algérie (94352)</t>
   </si>
   <si>
     <t/>
@@ -1027,7 +1051,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B113"/>
+  <dimension ref="A1:B117"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1927,15 +1951,47 @@
         <v>248</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>258</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-MARS-2026/ValueSet-JDV-J258-Departement.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-JDV-J258-Departement.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240628120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-28T12:00:00+01:00</t>
+    <t>2026-03-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-MARS-2026/ValueSet-JDV-J258-Departement.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-JDV-J258-Departement.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="251">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260330120000</t>
+    <t>20240628120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00+01:00</t>
+    <t>2024-06-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -757,30 +757,6 @@
   </si>
   <si>
     <t>La Passion-Clipperton (989)</t>
-  </si>
-  <si>
-    <t>91352</t>
-  </si>
-  <si>
-    <t>Département D'Alger et Orleansville (91352)</t>
-  </si>
-  <si>
-    <t>92352</t>
-  </si>
-  <si>
-    <t>Département D'Oran et Bou Sfer (92352)</t>
-  </si>
-  <si>
-    <t>93352</t>
-  </si>
-  <si>
-    <t>Département de Constantine (93352)</t>
-  </si>
-  <si>
-    <t>94352</t>
-  </si>
-  <si>
-    <t>Sud de l'Algérie (94352)</t>
   </si>
   <si>
     <t/>
@@ -1051,7 +1027,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B117"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1951,47 +1927,15 @@
         <v>248</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="B113" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>258</v>
       </c>
     </row>
   </sheetData>
